--- a/results/Int Task Remove ACC -1.0/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7043074594065284</v>
+        <v>0.7209303470757646</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6989379079220054</v>
+        <v>0.6825916580257665</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7043185389867566</v>
+        <v>0.6813282341470552</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7013796363646596</v>
+        <v>0.6705669720175529</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6992273839387591</v>
+        <v>0.6708453684540785</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6992273839387591</v>
+        <v>0.6705295124844006</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6958977062806799</v>
+        <v>0.6615671872779687</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.697289688463308</v>
+        <v>0.660399962294254</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.693338499114337</v>
+        <v>0.6579480336031358</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6951425361616395</v>
+        <v>0.6570379252272545</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6846009311068184</v>
+        <v>0.6582315301638934</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6838032013303939</v>
+        <v>0.6555923038070142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6799643905808795</v>
+        <v>0.6548320335637416</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6766074536381121</v>
+        <v>0.6586223051998756</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6809494180230652</v>
+        <v>0.6448319210092759</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6812541944125149</v>
+        <v>0.6466197783521181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6864364482312769</v>
+        <v>0.6426362295942271</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6871217994082448</v>
+        <v>0.6537073682374112</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6871217994082448</v>
+        <v>0.6599240679435032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6777312396326785</v>
+        <v>0.6608018169104644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6767998514281051</v>
+        <v>0.6661884274312116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6786847869977082</v>
+        <v>0.6724084685980075</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6837648624654775</v>
+        <v>0.6634035837341914</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6867310243722626</v>
+        <v>0.6634035837341914</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6850768254575691</v>
+        <v>0.6520633695711815</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6850393659244169</v>
+        <v>0.6620320020484913</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6894238899667542</v>
+        <v>0.6623478580181691</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6892476718812213</v>
+        <v>0.6402820825952809</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.669150368545529</v>
+        <v>0.6422197780707321</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6761486183235856</v>
+        <v>0.6276154843992476</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6613645892395117</v>
+        <v>0.6297302772919958</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6561805767572214</v>
+        <v>0.6160735515295448</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6546174766132924</v>
+        <v>0.5843848968790053</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6426021115217786</v>
+        <v>0.5926720711569333</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6470513543819564</v>
+        <v>0.5926720711569333</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6321201251605659</v>
+        <v>0.5897595484877604</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6264874776122134</v>
+        <v>0.591232429192689</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6357171196749427</v>
+        <v>0.5820129873784237</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6357171196749427</v>
+        <v>0.5878856924983855</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6421100374665678</v>
+        <v>0.5879606115646899</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6120986202229423</v>
+        <v>0.5837429846911857</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6128520316784544</v>
+        <v>0.5752472329188046</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6169905186931863</v>
+        <v>0.5696077265826917</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6169905186931863</v>
+        <v>0.544721582459512</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5998704568445075</v>
+        <v>0.544721582459512</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5869485007041688</v>
+        <v>0.5378782709382963</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.586803762695792</v>
+        <v>0.5378782709382963</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5862358902425127</v>
+        <v>0.5344958333743688</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5887567585439392</v>
+        <v>0.5101459057609596</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5938640932963968</v>
+        <v>0.5000666533477216</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5918736379150973</v>
+        <v>0.5261601199830606</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6097351523072962</v>
+        <v>0.5265134354858906</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6116839273629755</v>
+        <v>0.5265134354858906</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6295668974502193</v>
+        <v>0.5130081306532239</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6369337631038019</v>
+        <v>0.5072733047538786</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6299576724862015</v>
+        <v>0.4983178383352069</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6307826615473144</v>
+        <v>0.4975201085587823</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.621927614816107</v>
+        <v>0.4992015667581641</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5912231082759891</v>
+        <v>0.4832520713539036</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5912231082759891</v>
+        <v>0.5234245188648319</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5775109846123976</v>
+        <v>0.5208704118227211</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.580197870750893</v>
+        <v>0.4947616448146861</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5815098337429847</v>
+        <v>0.4951149603175161</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5358111378271642</v>
+        <v>0.4953235378119693</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.551149321788997</v>
+        <v>0.4986693951745086</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5189506547152583</v>
+        <v>0.5005270714594234</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5183342431485987</v>
+        <v>0.4926468519219379</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5190570538587188</v>
+        <v>0.4982088011964539</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.511829826089281</v>
+        <v>0.5008105680201811</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5109197177133997</v>
+        <v>0.5043973622860938</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5086065475746623</v>
+        <v>0.5024911468877987</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5125849962083214</v>
+        <v>0.4971530754804317</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5376295959153984</v>
+        <v>0.4991980494311075</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5275375052584039</v>
+        <v>0.497206714718044</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5276711636865526</v>
+        <v>0.4969283182815184</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5204975751547273</v>
+        <v>0.4968159396820618</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5065480319148188</v>
+        <v>0.4968117188895939</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5039897040802401</v>
+        <v>0.4871112826003458</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5040969825554648</v>
+        <v>0.4844456762905425</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.53745179503269</v>
+        <v>0.4762879396482954</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4837671839013348</v>
+        <v>0.4663618668283699</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.47464482031383</v>
+        <v>0.4663618668283699</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4855328820837208</v>
+        <v>0.4807575830054012</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4767188122127223</v>
+        <v>0.4706016528623304</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4767188122127223</v>
+        <v>0.4779565596039208</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4645996859730404</v>
+        <v>0.4696846856986889</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4645996859730404</v>
+        <v>0.4763704209677714</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5028727768734339</v>
+        <v>0.4763329614346192</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5063624929125859</v>
+        <v>0.4966064828558445</v>
       </c>
     </row>
   </sheetData>
